--- a/Memorial_Tunnel/Test_606A/SES_results/MT-T606A-R3.xlsx
+++ b/Memorial_Tunnel/Test_606A/SES_results/MT-T606A-R3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdaza\OneDrive\Documents\GitHub\SES_Validation\Memorial_Tunnel\Test_606A\SES_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D23E38EC-3DFB-4B4A-86EB-CD05A4AF13F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF552DD2-CFB7-43B5-AA85-FD395EA46CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2100" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F25E0DA8-0167-40DE-8283-5E3FA09DF007}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F25E0DA8-0167-40DE-8283-5E3FA09DF007}"/>
   </bookViews>
   <sheets>
     <sheet name="Flow Rate" sheetId="1" r:id="rId1"/>
@@ -989,9 +989,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED09F5F7-1360-4E96-8B1F-01D1E618388C}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:DB47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:106" x14ac:dyDescent="0.35">
       <c r="F1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>101</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="3" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>103</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="4" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>105</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="5" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>107</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="6" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="7" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>111</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="8" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>113</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="9" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>115</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="10" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>117</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="11" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>119</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="12" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>121</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="13" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>123</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="14" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>125</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="15" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>127</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="16" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>129</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="17" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>131</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="18" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>133</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="19" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>135</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="20" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>137</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="21" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>139</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="22" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>141</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="23" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>143</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="24" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>145</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="25" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>147</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="26" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>149</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="27" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>151</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="28" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>153</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="29" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>155</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="30" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>157</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="31" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>159</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="32" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>161</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="33" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>163</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="34" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>165</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="35" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="36" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>169</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="37" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>171</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="38" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>173</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="39" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>175</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="40" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>177</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="41" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>179</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="42" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>181</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="43" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>183</v>
       </c>
@@ -14610,7 +14610,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="44" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>185</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="45" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>187</v>
       </c>
@@ -15244,7 +15244,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="46" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>189</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>96.521455184760001</v>
       </c>
     </row>
-    <row r="47" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>191</v>
       </c>
@@ -15885,10 +15885,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7A12FC-2C1D-4C01-A45A-BC5D59A781DE}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:DB47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:106" x14ac:dyDescent="0.35">
       <c r="F1" t="s">
         <v>0</v>
       </c>
@@ -16193,7 +16194,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>101</v>
       </c>
@@ -16510,7 +16511,7 @@
         <v>2.8888888888888902</v>
       </c>
     </row>
-    <row r="3" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>103</v>
       </c>
@@ -16827,7 +16828,7 @@
         <v>2.9444444444444402</v>
       </c>
     </row>
-    <row r="4" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>105</v>
       </c>
@@ -17144,7 +17145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>107</v>
       </c>
@@ -17461,7 +17462,7 @@
         <v>3.1111111111111098</v>
       </c>
     </row>
-    <row r="6" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -17778,7 +17779,7 @@
         <v>3.1111111111111098</v>
       </c>
     </row>
-    <row r="7" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>111</v>
       </c>
@@ -18095,7 +18096,7 @@
         <v>3.1666666666666701</v>
       </c>
     </row>
-    <row r="8" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>113</v>
       </c>
@@ -18412,7 +18413,7 @@
         <v>3.2222222222222201</v>
       </c>
     </row>
-    <row r="9" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>115</v>
       </c>
@@ -18729,7 +18730,7 @@
         <v>3.2777777777777799</v>
       </c>
     </row>
-    <row r="10" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>117</v>
       </c>
@@ -19046,7 +19047,7 @@
         <v>3.3333333333333299</v>
       </c>
     </row>
-    <row r="11" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>119</v>
       </c>
@@ -19363,7 +19364,7 @@
         <v>3.3888888888888902</v>
       </c>
     </row>
-    <row r="12" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>121</v>
       </c>
@@ -19680,7 +19681,7 @@
         <v>3.44444444444445</v>
       </c>
     </row>
-    <row r="13" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>123</v>
       </c>
@@ -19997,7 +19998,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="14" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>125</v>
       </c>
@@ -20314,7 +20315,7 @@
         <v>3.55555555555555</v>
       </c>
     </row>
-    <row r="15" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>127</v>
       </c>
@@ -20631,7 +20632,7 @@
         <v>3.6111111111111098</v>
       </c>
     </row>
-    <row r="16" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>129</v>
       </c>
@@ -20948,7 +20949,7 @@
         <v>3.6111111111111098</v>
       </c>
     </row>
-    <row r="17" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>131</v>
       </c>
@@ -21265,7 +21266,7 @@
         <v>3.6666666666666701</v>
       </c>
     </row>
-    <row r="18" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>133</v>
       </c>
@@ -21582,7 +21583,7 @@
         <v>3.7222222222222201</v>
       </c>
     </row>
-    <row r="19" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>135</v>
       </c>
@@ -21899,7 +21900,7 @@
         <v>3.7777777777777799</v>
       </c>
     </row>
-    <row r="20" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>137</v>
       </c>
@@ -22216,7 +22217,7 @@
         <v>3.8333333333333299</v>
       </c>
     </row>
-    <row r="21" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>139</v>
       </c>
@@ -22533,7 +22534,7 @@
         <v>3.8333333333333299</v>
       </c>
     </row>
-    <row r="22" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>141</v>
       </c>
@@ -22850,7 +22851,7 @@
         <v>3.8888888888888902</v>
       </c>
     </row>
-    <row r="23" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>143</v>
       </c>
@@ -23167,7 +23168,7 @@
         <v>3.8888888888888902</v>
       </c>
     </row>
-    <row r="24" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>145</v>
       </c>
@@ -23484,7 +23485,7 @@
         <v>3.94444444444445</v>
       </c>
     </row>
-    <row r="25" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>147</v>
       </c>
@@ -23801,7 +23802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>149</v>
       </c>
@@ -24118,7 +24119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>151</v>
       </c>
@@ -24435,7 +24436,7 @@
         <v>4.05555555555555</v>
       </c>
     </row>
-    <row r="28" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>153</v>
       </c>
@@ -24752,7 +24753,7 @@
         <v>4.1111111111111098</v>
       </c>
     </row>
-    <row r="29" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>155</v>
       </c>
@@ -25069,7 +25070,7 @@
         <v>4.1111111111111098</v>
       </c>
     </row>
-    <row r="30" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>157</v>
       </c>
@@ -25386,7 +25387,7 @@
         <v>4.1666666666666696</v>
       </c>
     </row>
-    <row r="31" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>159</v>
       </c>
@@ -25703,7 +25704,7 @@
         <v>4.2222222222222197</v>
       </c>
     </row>
-    <row r="32" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>161</v>
       </c>
@@ -26020,7 +26021,7 @@
         <v>4.2222222222222197</v>
       </c>
     </row>
-    <row r="33" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>163</v>
       </c>
@@ -26337,7 +26338,7 @@
         <v>4.2777777777777803</v>
       </c>
     </row>
-    <row r="34" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>165</v>
       </c>
@@ -26654,7 +26655,7 @@
         <v>4.3333333333333304</v>
       </c>
     </row>
-    <row r="35" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -26971,7 +26972,7 @@
         <v>77.6666666666667</v>
       </c>
     </row>
-    <row r="36" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>169</v>
       </c>
@@ -27288,7 +27289,7 @@
         <v>75.5555555555556</v>
       </c>
     </row>
-    <row r="37" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>171</v>
       </c>
@@ -27605,7 +27606,7 @@
         <v>74.6111111111111</v>
       </c>
     </row>
-    <row r="38" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>173</v>
       </c>
@@ -27922,7 +27923,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>175</v>
       </c>
@@ -28239,7 +28240,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>177</v>
       </c>
@@ -28556,7 +28557,7 @@
         <v>70.1111111111111</v>
       </c>
     </row>
-    <row r="41" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>179</v>
       </c>
@@ -28873,7 +28874,7 @@
         <v>68.3333333333333</v>
       </c>
     </row>
-    <row r="42" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>181</v>
       </c>
@@ -29190,7 +29191,7 @@
         <v>66.6111111111111</v>
       </c>
     </row>
-    <row r="43" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>183</v>
       </c>
@@ -29507,7 +29508,7 @@
         <v>66.0555555555556</v>
       </c>
     </row>
-    <row r="44" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>185</v>
       </c>
@@ -29824,7 +29825,7 @@
         <v>64.4444444444444</v>
       </c>
     </row>
-    <row r="45" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>187</v>
       </c>
@@ -30141,7 +30142,7 @@
         <v>62.8333333333333</v>
       </c>
     </row>
-    <row r="46" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>189</v>
       </c>
@@ -30458,7 +30459,7 @@
         <v>61.1111111111111</v>
       </c>
     </row>
-    <row r="47" spans="2:106" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:106" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>191</v>
       </c>
